--- a/DataGenerationROBIN/data/TimetablesMAD-BCN-June2025.xlsx
+++ b/DataGenerationROBIN/data/TimetablesMAD-BCN-June2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseangel/UCLM/Proyectos/Investigación/Estancia UC3M 2025/DistributionalConstraintLearning/DataGenerationROBIN/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JC\Desktop\Descargas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8B6AC6-303B-EA4F-B3E1-8728C575E1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF374AB0-172C-4572-A11F-53F73A4FDD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2540" windowWidth="30240" windowHeight="17020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lunes" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="104">
   <si>
     <t>Hora Salida</t>
   </si>
@@ -314,13 +314,37 @@
   </si>
   <si>
     <t>Precio</t>
+  </si>
+  <si>
+    <t>Capacidad</t>
+  </si>
+  <si>
+    <t>Modelo de Tren</t>
+  </si>
+  <si>
+    <t>S-108</t>
+  </si>
+  <si>
+    <t>S-109</t>
+  </si>
+  <si>
+    <t>S-103</t>
+  </si>
+  <si>
+    <t>S-106</t>
+  </si>
+  <si>
+    <t>S-100</t>
+  </si>
+  <si>
+    <t>s-103</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,6 +360,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -345,7 +375,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -368,16 +398,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -682,15 +728,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,8 +751,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -717,8 +771,14 @@
       <c r="D2">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -731,8 +791,14 @@
       <c r="D3">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -745,8 +811,14 @@
       <c r="D4">
         <v>47.45</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -759,8 +831,14 @@
       <c r="D5">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -773,8 +851,14 @@
       <c r="D6">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -787,8 +871,14 @@
       <c r="D7">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -801,8 +891,14 @@
       <c r="D8">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>836</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -815,8 +911,14 @@
       <c r="D9">
         <v>61.15</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -829,8 +931,14 @@
       <c r="D10">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>581</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -843,8 +951,14 @@
       <c r="D11">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>826</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -857,8 +971,14 @@
       <c r="D12">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>378</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -871,8 +991,14 @@
       <c r="D13">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>414</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -885,8 +1011,14 @@
       <c r="D14">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>339</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -899,8 +1031,14 @@
       <c r="D15">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>291</v>
+      </c>
+      <c r="F15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -913,8 +1051,14 @@
       <c r="D16">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>414</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -927,8 +1071,14 @@
       <c r="D17">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>571</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -941,8 +1091,14 @@
       <c r="D18">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>414</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -955,8 +1111,14 @@
       <c r="D19">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -969,8 +1131,14 @@
       <c r="D20">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>414</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -983,8 +1151,14 @@
       <c r="D21">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -997,8 +1171,14 @@
       <c r="D22">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>414</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1011,8 +1191,14 @@
       <c r="D23">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>414</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1025,8 +1211,14 @@
       <c r="D24">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>414</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1039,8 +1231,14 @@
       <c r="D25">
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>581</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1053,8 +1251,14 @@
       <c r="D26">
         <v>20.350000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>414</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1067,8 +1271,14 @@
       <c r="D27">
         <v>17.25</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>414</v>
+      </c>
+      <c r="F27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1081,8 +1291,14 @@
       <c r="D28">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>414</v>
+      </c>
+      <c r="F28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.26527777777777778</v>
       </c>
@@ -1095,8 +1311,14 @@
       <c r="D30">
         <v>31.04</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>461</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.30694444444444446</v>
       </c>
@@ -1109,8 +1331,14 @@
       <c r="D31">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.35555555555555557</v>
       </c>
@@ -1123,8 +1351,14 @@
       <c r="D32">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0.39027777777777778</v>
       </c>
@@ -1137,8 +1371,14 @@
       <c r="D33">
         <v>48.96</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0.41458333333333336</v>
       </c>
@@ -1151,8 +1391,14 @@
       <c r="D34">
         <v>34.770000000000003</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0.47361111111111109</v>
       </c>
@@ -1165,8 +1411,14 @@
       <c r="D35">
         <v>31.04</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>461</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.51527777777777772</v>
       </c>
@@ -1179,8 +1431,14 @@
       <c r="D36">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.58472222222222225</v>
       </c>
@@ -1193,8 +1451,14 @@
       <c r="D37">
         <v>31.04</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>461</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.61250000000000004</v>
       </c>
@@ -1207,8 +1471,14 @@
       <c r="D38">
         <v>50.78</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>461</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.69236111111111109</v>
       </c>
@@ -1221,8 +1491,14 @@
       <c r="D39">
         <v>31.04</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>461</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.72361111111111109</v>
       </c>
@@ -1235,8 +1511,14 @@
       <c r="D40">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0.77222222222222225</v>
       </c>
@@ -1249,8 +1531,14 @@
       <c r="D41">
         <v>30.28</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0.81180555555555556</v>
       </c>
@@ -1263,8 +1551,14 @@
       <c r="D42">
         <v>56.49</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0.84861111111111109</v>
       </c>
@@ -1277,8 +1571,14 @@
       <c r="D43">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <v>461</v>
+      </c>
+      <c r="F43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0.29305555555555557</v>
       </c>
@@ -1291,8 +1591,14 @@
       <c r="D45">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>509</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0.41805555555555557</v>
       </c>
@@ -1305,8 +1611,14 @@
       <c r="D46">
         <v>33</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>509</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>0.59166666666666667</v>
       </c>
@@ -1319,8 +1631,14 @@
       <c r="D47">
         <v>29</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>509</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0.72013888888888888</v>
       </c>
@@ -1333,8 +1651,14 @@
       <c r="D48">
         <v>29</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>509</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>0.87638888888888888</v>
       </c>
@@ -1347,23 +1671,32 @@
       <c r="D49">
         <v>19</v>
       </c>
+      <c r="E49">
+        <v>509</v>
+      </c>
+      <c r="F49" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B02D58A8-5A01-694A-AA1C-FEFA0AD6B2F9}">
-  <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="18.1640625" customWidth="1"/>
+    <col min="3" max="3" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1376,8 +1709,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1390,8 +1729,14 @@
       <c r="D2">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1404,8 +1749,14 @@
       <c r="D3">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1418,8 +1769,14 @@
       <c r="D4">
         <v>94.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1432,8 +1789,14 @@
       <c r="D5">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1446,8 +1809,14 @@
       <c r="D6">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1460,8 +1829,14 @@
       <c r="D7">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1474,8 +1849,14 @@
       <c r="D8">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>414</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1488,8 +1869,14 @@
       <c r="D9">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -1502,8 +1889,14 @@
       <c r="D10">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>581</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1516,8 +1909,14 @@
       <c r="D11">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>826</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -1530,8 +1929,14 @@
       <c r="D12">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>378</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1544,8 +1949,14 @@
       <c r="D13">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>414</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1558,8 +1969,14 @@
       <c r="D14">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>339</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1572,8 +1989,14 @@
       <c r="D15">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>291</v>
+      </c>
+      <c r="F15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1586,8 +2009,14 @@
       <c r="D16">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>414</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1600,8 +2029,14 @@
       <c r="D17">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>571</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1614,8 +2049,14 @@
       <c r="D18">
         <v>27.1</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>414</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1628,8 +2069,14 @@
       <c r="D19">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1642,8 +2089,14 @@
       <c r="D20">
         <v>47.45</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>414</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1656,8 +2109,14 @@
       <c r="D21">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1670,8 +2129,14 @@
       <c r="D22">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>414</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1684,8 +2149,14 @@
       <c r="D23">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>414</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1698,8 +2169,14 @@
       <c r="D24">
         <v>27.1</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>414</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1712,8 +2189,14 @@
       <c r="D25">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>581</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1726,8 +2209,14 @@
       <c r="D26">
         <v>33.9</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>414</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -1740,8 +2229,14 @@
       <c r="D27">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>414</v>
+      </c>
+      <c r="F27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -1754,8 +2249,14 @@
       <c r="D28">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>414</v>
+      </c>
+      <c r="F28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.26527777777777778</v>
       </c>
@@ -1768,8 +2269,14 @@
       <c r="D30">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>461</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.30694444444444446</v>
       </c>
@@ -1782,8 +2289,14 @@
       <c r="D31">
         <v>27.58</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.35555555555555557</v>
       </c>
@@ -1796,8 +2309,14 @@
       <c r="D32">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0.39027777777777778</v>
       </c>
@@ -1810,8 +2329,14 @@
       <c r="D33">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0.41458333333333336</v>
       </c>
@@ -1824,8 +2349,14 @@
       <c r="D34">
         <v>36.89</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0.47361111111111109</v>
       </c>
@@ -1838,8 +2369,14 @@
       <c r="D35">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>461</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.51527777777777772</v>
       </c>
@@ -1852,8 +2389,14 @@
       <c r="D36">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.58472222222222225</v>
       </c>
@@ -1866,8 +2409,14 @@
       <c r="D37">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>461</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.61250000000000004</v>
       </c>
@@ -1880,8 +2429,14 @@
       <c r="D38">
         <v>31.82</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>461</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.69236111111111109</v>
       </c>
@@ -1894,8 +2449,14 @@
       <c r="D39">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>461</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.72361111111111109</v>
       </c>
@@ -1908,8 +2469,14 @@
       <c r="D40">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0.77222222222222225</v>
       </c>
@@ -1922,8 +2489,14 @@
       <c r="D41">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0.81180555555555556</v>
       </c>
@@ -1936,8 +2509,14 @@
       <c r="D42">
         <v>34.770000000000003</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0.84861111111111109</v>
       </c>
@@ -1950,8 +2529,14 @@
       <c r="D43">
         <v>26.78</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <v>461</v>
+      </c>
+      <c r="F43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>85</v>
       </c>
@@ -1964,8 +2549,14 @@
       <c r="D45">
         <v>29</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>509</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>87</v>
       </c>
@@ -1978,8 +2569,14 @@
       <c r="D46">
         <v>29</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>509</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>89</v>
       </c>
@@ -1992,8 +2589,14 @@
       <c r="D47">
         <v>29</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>509</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>91</v>
       </c>
@@ -2006,8 +2609,14 @@
       <c r="D48">
         <v>33</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>509</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>93</v>
       </c>
@@ -2020,22 +2629,30 @@
       <c r="D49">
         <v>29</v>
       </c>
+      <c r="E49">
+        <v>509</v>
+      </c>
+      <c r="F49" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4F2C69A-1622-7240-8EB5-CB15974B6D06}">
-  <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2048,8 +2665,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2062,8 +2685,14 @@
       <c r="D2">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2076,8 +2705,14 @@
       <c r="D3">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2090,8 +2725,14 @@
       <c r="D4">
         <v>81.349999999999994</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2104,8 +2745,14 @@
       <c r="D5">
         <v>28.75</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2118,8 +2765,14 @@
       <c r="D6">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2132,8 +2785,14 @@
       <c r="D7">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2146,8 +2805,14 @@
       <c r="D8">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>414</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2160,8 +2825,14 @@
       <c r="D9">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2174,8 +2845,14 @@
       <c r="D10">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>581</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2188,8 +2865,14 @@
       <c r="D11">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>826</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -2202,8 +2885,14 @@
       <c r="D12">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>378</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2216,8 +2905,14 @@
       <c r="D13">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>414</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2230,8 +2925,14 @@
       <c r="D14">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>339</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2244,8 +2945,14 @@
       <c r="D15">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>291</v>
+      </c>
+      <c r="F15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2258,8 +2965,14 @@
       <c r="D16">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>414</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2272,8 +2985,14 @@
       <c r="D17">
         <v>29</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>571</v>
+      </c>
+      <c r="F17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2286,8 +3005,14 @@
       <c r="D18">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>414</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2300,8 +3025,14 @@
       <c r="D19">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2314,8 +3045,14 @@
       <c r="D20">
         <v>108.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>414</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2328,8 +3065,14 @@
       <c r="D21">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2342,8 +3085,14 @@
       <c r="D22">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>414</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2356,8 +3105,14 @@
       <c r="D23">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>414</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2370,8 +3125,14 @@
       <c r="D24">
         <v>94.9</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>414</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2384,8 +3145,14 @@
       <c r="D25">
         <v>25</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>581</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2398,8 +3165,14 @@
       <c r="D26">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>414</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2412,8 +3185,14 @@
       <c r="D27">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>414</v>
+      </c>
+      <c r="F27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2426,8 +3205,14 @@
       <c r="D28">
         <v>45.85</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>414</v>
+      </c>
+      <c r="F28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.26527777777777778</v>
       </c>
@@ -2440,8 +3225,14 @@
       <c r="D30">
         <v>27.58</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>461</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.30694444444444446</v>
       </c>
@@ -2454,8 +3245,14 @@
       <c r="D31">
         <v>28.41</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.35555555555555557</v>
       </c>
@@ -2468,8 +3265,14 @@
       <c r="D32">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0.39027777777777778</v>
       </c>
@@ -2482,8 +3285,14 @@
       <c r="D33">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0.41458333333333336</v>
       </c>
@@ -2496,8 +3305,14 @@
       <c r="D34">
         <v>34.770000000000003</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0.47361111111111109</v>
       </c>
@@ -2510,8 +3325,14 @@
       <c r="D35">
         <v>39.56</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>461</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.51527777777777772</v>
       </c>
@@ -2524,8 +3345,14 @@
       <c r="D36">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.58472222222222225</v>
       </c>
@@ -2538,8 +3365,14 @@
       <c r="D37">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>461</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.61250000000000004</v>
       </c>
@@ -2552,8 +3385,14 @@
       <c r="D38">
         <v>50.78</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>461</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.69236111111111109</v>
       </c>
@@ -2566,8 +3405,14 @@
       <c r="D39">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>461</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.72361111111111109</v>
       </c>
@@ -2580,8 +3425,14 @@
       <c r="D40">
         <v>31.2</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0.77222222222222225</v>
       </c>
@@ -2594,8 +3445,14 @@
       <c r="D41">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0.81180555555555556</v>
       </c>
@@ -2608,8 +3465,14 @@
       <c r="D42">
         <v>34.770000000000003</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>0.84861111111111109</v>
       </c>
@@ -2622,8 +3485,14 @@
       <c r="D43">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <v>461</v>
+      </c>
+      <c r="F43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0.29305555555555557</v>
       </c>
@@ -2636,8 +3505,14 @@
       <c r="D45">
         <v>33</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>509</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0.41805555555555557</v>
       </c>
@@ -2650,8 +3525,14 @@
       <c r="D46">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>509</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>0.59166666666666667</v>
       </c>
@@ -2664,8 +3545,14 @@
       <c r="D47">
         <v>33</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>509</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0.72013888888888888</v>
       </c>
@@ -2678,8 +3565,14 @@
       <c r="D48">
         <v>39</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E48">
+        <v>509</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>0.87638888888888888</v>
       </c>
@@ -2692,23 +3585,31 @@
       <c r="D49">
         <v>33</v>
       </c>
+      <c r="E49">
+        <v>509</v>
+      </c>
+      <c r="F49" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2B75100-1934-E144-941B-4D26C8A5EBA2}">
-  <dimension ref="A1:D49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2721,8 +3622,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +3642,14 @@
       <c r="D2">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -2749,8 +3662,14 @@
       <c r="D3">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>359</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2763,8 +3682,14 @@
       <c r="D4">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -2777,8 +3702,14 @@
       <c r="D5">
         <v>34.450000000000003</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -2791,8 +3722,14 @@
       <c r="D6">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2805,8 +3742,14 @@
       <c r="D7">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2819,8 +3762,14 @@
       <c r="D8">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>414</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2833,8 +3782,14 @@
       <c r="D9">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>414</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2847,8 +3802,14 @@
       <c r="D10">
         <v>45</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>581</v>
+      </c>
+      <c r="F10" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -2861,8 +3822,14 @@
       <c r="D11">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>826</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -2875,8 +3842,14 @@
       <c r="D12">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>378</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2889,8 +3862,14 @@
       <c r="D13">
         <v>47.45</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>414</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2903,485 +3882,709 @@
       <c r="D14">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="E14">
+        <v>339</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>0.58125000000000004</v>
+      </c>
+      <c r="B15" s="4">
+        <v>0.69027777777777777</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5">
+        <v>414</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>41</v>
       </c>
-      <c r="C15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15">
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="E16">
+        <v>291</v>
+      </c>
+      <c r="F16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16">
+      <c r="C17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="E17">
+        <v>414</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>43</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>54</v>
       </c>
-      <c r="D17">
+      <c r="D18">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="E18">
+        <v>571</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>44</v>
       </c>
-      <c r="C18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18">
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19">
         <v>81.349999999999994</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>45</v>
       </c>
-      <c r="C19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19">
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="E20">
+        <v>414</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>25</v>
       </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20">
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21">
         <v>122.05</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>46</v>
       </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21">
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="E22">
+        <v>414</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="C22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D22">
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="E23">
+        <v>414</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C23" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23">
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="E24">
+        <v>414</v>
+      </c>
+      <c r="F24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>49</v>
       </c>
-      <c r="C24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24">
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="E25">
+        <v>414</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>50</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>54</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <v>29</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="E26">
+        <v>581</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="C26" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26">
+      <c r="C27" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27">
         <v>47.45</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="E27">
+        <v>414</v>
+      </c>
+      <c r="F27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="C27" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27">
+      <c r="C28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="E28">
+        <v>414</v>
+      </c>
+      <c r="F28" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>53</v>
       </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28">
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29">
         <v>45.85</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="2">
+      <c r="E29">
+        <v>414</v>
+      </c>
+      <c r="F29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>0.26527777777777778</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B31" s="2">
         <v>0.37430555555555556</v>
       </c>
-      <c r="C30" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30">
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
         <v>0.30694444444444446</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B32" s="2">
         <v>0.41597222222222224</v>
       </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31">
+      <c r="C32" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32">
         <v>31.04</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>0.35555555555555557</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B33" s="2">
         <v>0.46458333333333335</v>
       </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32">
+      <c r="C33" t="s">
+        <v>84</v>
+      </c>
+      <c r="D33">
         <v>44.01</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>0.39027777777777778</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B34" s="2">
         <v>0.50972222222222219</v>
       </c>
-      <c r="C33" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33">
+      <c r="C34" t="s">
+        <v>84</v>
+      </c>
+      <c r="D34">
         <v>55.5</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
         <v>0.41458333333333336</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B35" s="2">
         <v>0.53402777777777777</v>
       </c>
-      <c r="C34" t="s">
-        <v>84</v>
-      </c>
-      <c r="D34">
+      <c r="C35" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35">
         <v>50.78</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="2">
+      <c r="E35">
+        <v>461</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>0.47361111111111109</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B36" s="2">
         <v>0.59305555555555556</v>
       </c>
-      <c r="C35" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35">
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36">
         <v>54.46</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
+      <c r="E36">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
         <v>0.51527777777777772</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B37" s="2">
         <v>0.63472222222222219</v>
       </c>
-      <c r="C36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36">
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37">
         <v>48.96</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="2">
+      <c r="E37">
+        <v>461</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
         <v>0.58472222222222225</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B38" s="2">
         <v>0.70416666666666672</v>
       </c>
-      <c r="C37" t="s">
-        <v>84</v>
-      </c>
-      <c r="D37">
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+      <c r="D38">
         <v>39.56</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="2">
+      <c r="E38">
+        <v>461</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
         <v>0.61250000000000004</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B39" s="2">
         <v>0.7368055555555556</v>
       </c>
-      <c r="C38" t="s">
-        <v>84</v>
-      </c>
-      <c r="D38">
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39">
         <v>41.04</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="2">
+      <c r="E39">
+        <v>461</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>0.69236111111111109</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B40" s="2">
         <v>0.80138888888888893</v>
       </c>
-      <c r="C39" t="s">
-        <v>84</v>
-      </c>
-      <c r="D39">
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40">
         <v>39.56</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="2">
+      <c r="E40">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
         <v>0.72361111111111109</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B41" s="2">
         <v>0.84305555555555556</v>
       </c>
-      <c r="C40" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40">
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41">
         <v>54.46</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="2">
+      <c r="E41">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>0.77222222222222225</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B42" s="2">
         <v>0.88124999999999998</v>
       </c>
-      <c r="C41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41">
+      <c r="C42" t="s">
+        <v>84</v>
+      </c>
+      <c r="D42">
         <v>32.58</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="2">
+      <c r="E42">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
         <v>0.81180555555555556</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B43" s="2">
         <v>0.93125000000000002</v>
       </c>
-      <c r="C42" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42">
+      <c r="C43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D43">
         <v>41.04</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="2">
+      <c r="E43">
+        <v>461</v>
+      </c>
+      <c r="F43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
         <v>0.84861111111111109</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B44" s="2">
         <v>0.96805555555555556</v>
       </c>
-      <c r="C43" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43">
+      <c r="C44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D44">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="2">
+      <c r="E44">
+        <v>461</v>
+      </c>
+      <c r="F44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>0.29305555555555557</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B46" s="2">
         <v>0.41249999999999998</v>
-      </c>
-      <c r="C45" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="2">
-        <v>0.41805555555555557</v>
-      </c>
-      <c r="B46" s="2">
-        <v>0.5444444444444444</v>
       </c>
       <c r="C46" t="s">
         <v>59</v>
       </c>
       <c r="D46">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+      <c r="E46">
+        <v>509</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>0.59166666666666667</v>
+        <v>0.41805555555555557</v>
       </c>
       <c r="B47" s="2">
-        <v>0.7006944444444444</v>
+        <v>0.5444444444444444</v>
       </c>
       <c r="C47" t="s">
         <v>59</v>
       </c>
       <c r="D47">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+      <c r="E47">
+        <v>509</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>0.72013888888888888</v>
+        <v>0.59166666666666667</v>
       </c>
       <c r="B48" s="2">
-        <v>0.82916666666666672</v>
+        <v>0.7006944444444444</v>
       </c>
       <c r="C48" t="s">
         <v>59</v>
       </c>
       <c r="D48">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+      <c r="E48">
+        <v>509</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>0.87638888888888888</v>
+        <v>0.72013888888888888</v>
       </c>
       <c r="B49" s="2">
-        <v>0.99583333333333335</v>
+        <v>0.82916666666666672</v>
       </c>
       <c r="C49" t="s">
         <v>59</v>
       </c>
       <c r="D49">
+        <v>39</v>
+      </c>
+      <c r="E49">
+        <v>509</v>
+      </c>
+      <c r="F49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>0.87638888888888888</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.99583333333333335</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50">
         <v>33</v>
       </c>
+      <c r="E50">
+        <v>509</v>
+      </c>
+      <c r="F50" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD8B13FD-8297-754B-8315-EB877195E0BF}">
-  <dimension ref="A1:D48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3394,8 +4597,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -3408,8 +4617,14 @@
       <c r="D2">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>527</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -3422,8 +4637,14 @@
       <c r="D3">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>414</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3436,8 +4657,14 @@
       <c r="D4">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -3450,8 +4677,14 @@
       <c r="D5">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3464,8 +4697,14 @@
       <c r="D6">
         <v>94.9</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -3478,8 +4717,14 @@
       <c r="D7">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>414</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -3492,8 +4737,14 @@
       <c r="D8">
         <v>49</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>581</v>
+      </c>
+      <c r="F8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3506,8 +4757,14 @@
       <c r="D9">
         <v>91.9</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>826</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -3520,8 +4777,14 @@
       <c r="D10">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>378</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -3534,8 +4797,14 @@
       <c r="D11">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>414</v>
+      </c>
+      <c r="F11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -3548,8 +4817,14 @@
       <c r="D12">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>339</v>
+      </c>
+      <c r="F12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -3562,8 +4837,14 @@
       <c r="D13">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="5">
+        <v>414</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -3576,8 +4857,14 @@
       <c r="D14">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>291</v>
+      </c>
+      <c r="F14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -3590,8 +4877,14 @@
       <c r="D15">
         <v>81.349999999999994</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>414</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -3604,8 +4897,14 @@
       <c r="D16">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>547</v>
+      </c>
+      <c r="F16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -3618,8 +4917,14 @@
       <c r="D17">
         <v>81.349999999999994</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>414</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -3632,8 +4937,14 @@
       <c r="D18">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>414</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -3646,8 +4957,14 @@
       <c r="D19">
         <v>81.349999999999994</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -3660,8 +4977,14 @@
       <c r="D20">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>581</v>
+      </c>
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -3674,8 +4997,14 @@
       <c r="D21">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -3688,8 +5017,14 @@
       <c r="D22">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>836</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -3702,8 +5037,14 @@
       <c r="D23">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>414</v>
+      </c>
+      <c r="F23" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -3716,8 +5057,14 @@
       <c r="D24">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>581</v>
+      </c>
+      <c r="F24" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -3730,8 +5077,14 @@
       <c r="D25">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>414</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -3744,8 +5097,14 @@
       <c r="D26">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>414</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -3758,8 +5117,14 @@
       <c r="D27">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>414</v>
+      </c>
+      <c r="F27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0.26527777777777778</v>
       </c>
@@ -3772,8 +5137,14 @@
       <c r="D29">
         <v>27.58</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>461</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.30694444444444446</v>
       </c>
@@ -3786,8 +5157,14 @@
       <c r="D30">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>461</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.35555555555555557</v>
       </c>
@@ -3800,8 +5177,14 @@
       <c r="D31">
         <v>32.590000000000003</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.39027777777777778</v>
       </c>
@@ -3814,8 +5197,14 @@
       <c r="D32">
         <v>44.01</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>0.41458333333333336</v>
       </c>
@@ -3828,8 +5217,14 @@
       <c r="D33">
         <v>57.59</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>0.47361111111111109</v>
       </c>
@@ -3842,8 +5237,14 @@
       <c r="D34">
         <v>48.96</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>0.51527777777777772</v>
       </c>
@@ -3856,8 +5257,14 @@
       <c r="D35">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <v>461</v>
+      </c>
+      <c r="F35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.58472222222222225</v>
       </c>
@@ -3870,8 +5277,14 @@
       <c r="D36">
         <v>54.46</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>461</v>
+      </c>
+      <c r="F36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.61250000000000004</v>
       </c>
@@ -3884,8 +5297,14 @@
       <c r="D37">
         <v>80.099999999999994</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>461</v>
+      </c>
+      <c r="F37" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.69236111111111109</v>
       </c>
@@ -3898,8 +5317,14 @@
       <c r="D38">
         <v>54.46</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>461</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.72361111111111109</v>
       </c>
@@ -3912,8 +5337,14 @@
       <c r="D39">
         <v>60.58</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>461</v>
+      </c>
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.77222222222222225</v>
       </c>
@@ -3926,8 +5357,14 @@
       <c r="D40">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <v>461</v>
+      </c>
+      <c r="F40" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>0.81180555555555556</v>
       </c>
@@ -3940,8 +5377,14 @@
       <c r="D41">
         <v>62.84</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <v>461</v>
+      </c>
+      <c r="F41" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>0.84861111111111109</v>
       </c>
@@ -3954,8 +5397,14 @@
       <c r="D42">
         <v>29.26</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <v>461</v>
+      </c>
+      <c r="F42" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>0.29305555555555557</v>
       </c>
@@ -3968,8 +5417,14 @@
       <c r="D44">
         <v>29</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44">
+        <v>509</v>
+      </c>
+      <c r="F44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>0.41805555555555557</v>
       </c>
@@ -3982,8 +5437,14 @@
       <c r="D45">
         <v>42</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E45">
+        <v>509</v>
+      </c>
+      <c r="F45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>0.59166666666666667</v>
       </c>
@@ -3996,8 +5457,14 @@
       <c r="D46">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E46">
+        <v>509</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>0.72013888888888888</v>
       </c>
@@ -4010,8 +5477,14 @@
       <c r="D47">
         <v>35</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E47">
+        <v>509</v>
+      </c>
+      <c r="F47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>0.87638888888888888</v>
       </c>
@@ -4024,18 +5497,28 @@
       <c r="D48">
         <v>19</v>
       </c>
+      <c r="E48">
+        <v>509</v>
+      </c>
+      <c r="F48" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0A110D8-F297-9B4A-89CD-54BC0EEDC8B0}">
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F32"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4048,8 +5531,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4062,8 +5551,14 @@
       <c r="D2">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4076,8 +5571,14 @@
       <c r="D3">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>414</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4090,8 +5591,14 @@
       <c r="D4">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4104,8 +5611,14 @@
       <c r="D5">
         <v>47.45</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>836</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -4118,8 +5631,14 @@
       <c r="D6">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>414</v>
+      </c>
+      <c r="F6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -4132,8 +5651,14 @@
       <c r="D7">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>581</v>
+      </c>
+      <c r="F7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -4146,8 +5671,14 @@
       <c r="D8">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>803</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -4160,8 +5691,14 @@
       <c r="D9">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>378</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4174,8 +5711,14 @@
       <c r="D10">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>339</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -4188,8 +5731,14 @@
       <c r="D11">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>547</v>
+      </c>
+      <c r="F11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4202,8 +5751,14 @@
       <c r="D12">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>414</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -4216,8 +5771,14 @@
       <c r="D13">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>581</v>
+      </c>
+      <c r="F13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -4230,8 +5791,14 @@
       <c r="D14">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>414</v>
+      </c>
+      <c r="F14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -4244,8 +5811,14 @@
       <c r="D15">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>581</v>
+      </c>
+      <c r="F15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -4258,8 +5831,14 @@
       <c r="D16">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>414</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>0.33819444444444446</v>
       </c>
@@ -4272,8 +5851,14 @@
       <c r="D18">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>461</v>
+      </c>
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>0.39027777777777778</v>
       </c>
@@ -4286,8 +5871,14 @@
       <c r="D19">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>461</v>
+      </c>
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>0.41458333333333336</v>
       </c>
@@ -4300,8 +5891,14 @@
       <c r="D20">
         <v>41.04</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>461</v>
+      </c>
+      <c r="F20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>0.47361111111111109</v>
       </c>
@@ -4314,8 +5911,14 @@
       <c r="D21">
         <v>35.57</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>461</v>
+      </c>
+      <c r="F21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>0.51527777777777772</v>
       </c>
@@ -4328,8 +5931,14 @@
       <c r="D22">
         <v>31.2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <v>461</v>
+      </c>
+      <c r="F22" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>0.61250000000000004</v>
       </c>
@@ -4342,8 +5951,14 @@
       <c r="D23">
         <v>34.770000000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>461</v>
+      </c>
+      <c r="F23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>0.69236111111111109</v>
       </c>
@@ -4356,8 +5971,14 @@
       <c r="D24">
         <v>30.14</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>461</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>0.81180555555555556</v>
       </c>
@@ -4370,8 +5991,14 @@
       <c r="D25">
         <v>33.76</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>461</v>
+      </c>
+      <c r="F25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>0.84861111111111109</v>
       </c>
@@ -4384,8 +6011,14 @@
       <c r="D26">
         <v>31.97</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>461</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>0.29305555555555557</v>
       </c>
@@ -4398,8 +6031,14 @@
       <c r="D28">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>509</v>
+      </c>
+      <c r="F28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>0.41805555555555557</v>
       </c>
@@ -4412,8 +6051,14 @@
       <c r="D29">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>509</v>
+      </c>
+      <c r="F29" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>0.59166666666666667</v>
       </c>
@@ -4426,8 +6071,14 @@
       <c r="D30">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>509</v>
+      </c>
+      <c r="F30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>0.72013888888888888</v>
       </c>
@@ -4440,8 +6091,14 @@
       <c r="D31">
         <v>22</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>509</v>
+      </c>
+      <c r="F31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>0.87638888888888888</v>
       </c>
@@ -4454,18 +6111,28 @@
       <c r="D32">
         <v>22</v>
       </c>
+      <c r="E32">
+        <v>509</v>
+      </c>
+      <c r="F32" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{138976AE-7570-4B4C-BA27-31FBD3999B9B}">
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4478,8 +6145,14 @@
       <c r="D1" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4492,8 +6165,14 @@
       <c r="D2">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <v>581</v>
+      </c>
+      <c r="F2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4506,8 +6185,14 @@
       <c r="D3">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <v>414</v>
+      </c>
+      <c r="F3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4520,8 +6205,14 @@
       <c r="D4">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <v>414</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -4534,8 +6225,14 @@
       <c r="D5">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E5">
+        <v>414</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -4548,8 +6245,14 @@
       <c r="D6">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E6">
+        <v>581</v>
+      </c>
+      <c r="F6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -4562,8 +6265,14 @@
       <c r="D7">
         <v>114.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <v>803</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>0.51875000000000004</v>
       </c>
@@ -4576,8 +6285,14 @@
       <c r="D8">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <v>398</v>
+      </c>
+      <c r="F8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -4590,8 +6305,14 @@
       <c r="D9">
         <v>45.95</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E9">
+        <v>339</v>
+      </c>
+      <c r="F9" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -4604,8 +6325,14 @@
       <c r="D10">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <v>381</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -4618,8 +6345,14 @@
       <c r="D11">
         <v>55</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <v>571</v>
+      </c>
+      <c r="F11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4632,8 +6365,14 @@
       <c r="D12">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <v>414</v>
+      </c>
+      <c r="F12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4646,8 +6385,14 @@
       <c r="D13">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <v>414</v>
+      </c>
+      <c r="F13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4660,8 +6405,14 @@
       <c r="D14">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <v>581</v>
+      </c>
+      <c r="F14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4674,8 +6425,14 @@
       <c r="D15">
         <v>57.45</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15">
+        <v>414</v>
+      </c>
+      <c r="F15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4688,8 +6445,14 @@
       <c r="D16">
         <v>80.45</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <v>414</v>
+      </c>
+      <c r="F16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4702,8 +6465,14 @@
       <c r="D17">
         <v>94.9</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <v>414</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4716,8 +6485,14 @@
       <c r="D18">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <v>581</v>
+      </c>
+      <c r="F18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4730,8 +6505,14 @@
       <c r="D19">
         <v>54.25</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <v>414</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4744,8 +6525,14 @@
       <c r="D20">
         <v>68.95</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <v>834</v>
+      </c>
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4758,8 +6545,14 @@
       <c r="D21">
         <v>103.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <v>414</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -4772,8 +6565,14 @@
       <c r="D23">
         <v>48.96</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <v>461</v>
+      </c>
+      <c r="F23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -4786,8 +6585,14 @@
       <c r="D24">
         <v>44.01</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <v>461</v>
+      </c>
+      <c r="F24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>64</v>
       </c>
@@ -4800,8 +6605,14 @@
       <c r="D25">
         <v>62.84</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <v>461</v>
+      </c>
+      <c r="F25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -4814,8 +6625,14 @@
       <c r="D26">
         <v>48.96</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <v>461</v>
+      </c>
+      <c r="F26" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -4828,8 +6645,14 @@
       <c r="D27">
         <v>60.58</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <v>461</v>
+      </c>
+      <c r="F27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -4842,8 +6665,14 @@
       <c r="D28">
         <v>85.9</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <v>461</v>
+      </c>
+      <c r="F28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -4856,8 +6685,14 @@
       <c r="D29">
         <v>77.760000000000005</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29">
+        <v>461</v>
+      </c>
+      <c r="F29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -4870,8 +6705,14 @@
       <c r="D30">
         <v>91.13</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <v>461</v>
+      </c>
+      <c r="F30" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -4884,8 +6725,14 @@
       <c r="D31">
         <v>88.48</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <v>461</v>
+      </c>
+      <c r="F31" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -4898,8 +6745,14 @@
       <c r="D32">
         <v>88.48</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <v>461</v>
+      </c>
+      <c r="F32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -4912,8 +6765,14 @@
       <c r="D33">
         <v>90.15</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <v>461</v>
+      </c>
+      <c r="F33" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>82</v>
       </c>
@@ -4926,8 +6785,14 @@
       <c r="D34">
         <v>85.9</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <v>461</v>
+      </c>
+      <c r="F34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>0.29305555555555557</v>
       </c>
@@ -4940,8 +6805,14 @@
       <c r="D36">
         <v>39</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <v>509</v>
+      </c>
+      <c r="F36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>0.41805555555555557</v>
       </c>
@@ -4954,8 +6825,14 @@
       <c r="D37">
         <v>42</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37">
+        <v>509</v>
+      </c>
+      <c r="F37" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>0.59166666666666667</v>
       </c>
@@ -4968,8 +6845,14 @@
       <c r="D38">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <v>509</v>
+      </c>
+      <c r="F38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>0.72013888888888888</v>
       </c>
@@ -4982,8 +6865,14 @@
       <c r="D39">
         <v>55</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39">
+        <v>509</v>
+      </c>
+      <c r="F39" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>0.87638888888888888</v>
       </c>
@@ -4996,8 +6885,15 @@
       <c r="D40">
         <v>49</v>
       </c>
+      <c r="E40">
+        <v>509</v>
+      </c>
+      <c r="F40" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>